--- a/assets/docs/lop5/Khoa hoc - Lop 5.xlsx
+++ b/assets/docs/lop5/Khoa hoc - Lop 5.xlsx
@@ -1044,19 +1044,19 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập giữa học kì I</t>
+          <t>Bài 9. Mạch điện đơn giản. Vật dẫn điện và vật cách điện (Tiết 1)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1064,7 +1064,13 @@
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.
+STEM: Đèn ngủ mini – mạch điện đơn giản (Khoa học – Công nghệ – Toán) — dạy thay cho tiết này.
+KNS: KN an toàn khi thực hành: làm đúng hướng dẫn, không tự ý thử nghiệm nguy hiểm.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1074,27 +1080,28 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 9. Mạch điện đơn giản. Vật dẫn điện và vật cách điện (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.
+STEM: Đèn ngủ mini – mạch điện đơn giản (Khoa học – Công nghệ – Toán) — dạy thay cho tiết này.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1111,7 +1118,7 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Mạch điện đơn giản. Vật dẫn điện và vật cách điện (Tiết 1)</t>
+          <t>Bài 10. Năng lượng chất đốt (Tiết 1)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1127,8 +1134,7 @@
       <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.
-STEM: Mạch điện đơn giản (Khoa học – Công nghệ) — dạy thay cho tiết này.
-KNS: KN an toàn khi thực hành: làm đúng hướng dẫn, không tự ý thử nghiệm nguy hiểm.</t>
+KNS: KN sử dụng tiết kiệm tài nguyên, năng lượng trong sinh hoạt hằng ngày.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1153,7 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Mạch điện đơn giản. Vật dẫn điện và vật cách điện (Tiết 2)</t>
+          <t>Bài 10. Năng lượng chất đốt (Tiết 2)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
@@ -1177,12 +1183,12 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Năng lượng chất đốt (Tiết 1)</t>
+          <t>Bài 11. Sử dụng năng lượng mặt trời, năng lượng gió, năng lượng nước chảy (Tiết 1)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1212,7 +1218,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Năng lượng chất đốt (Tiết 2)</t>
+          <t>Bài 11. Sử dụng năng lượng mặt trời, năng lượng gió, năng lượng nước chảy (Tiết 2)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -1223,7 +1229,8 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.</t>
+          <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.
+STEM: Mô hình thuyền buồm (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1242,25 +1249,16 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Sử dụng năng lượng mặt trời, năng lượng gió, năng lượng nước chảy (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 11. Sử dụng năng lượng mặt trời, năng lượng gió, năng lượng nước chảy (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.
-KNS: KN sử dụng tiết kiệm tài nguyên, năng lượng trong sinh hoạt hằng ngày.</t>
-        </is>
-      </c>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1277,21 +1275,20 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Sử dụng năng lượng mặt trời, năng lượng gió, năng lượng nước chảy (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
+          <t>Bài 12. Ôn tập chủ đề Năng lượng</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS lắp thử mạch điện trên phần mềm mô phỏng.
-STEM: Mô hình thuyền buồm (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
-        </is>
-      </c>
+      <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1301,23 +1298,31 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Năng lượng</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Sử dụng năng lượng mặt trời, năng lượng gió, năng lượng nước chảy (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>Bài 13. Sinh sản của thực vật có hoa (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1327,27 +1332,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Năng lượng</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Ôn tập chủ đề Năng lượng</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 13. Sinh sản của thực vật có hoa (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1364,12 +1369,12 @@
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Sinh sản của thực vật có hoa (Tiết 1)</t>
+          <t>Bài 14. Sự phát triển của cây con (Tiết 1)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1379,7 +1384,8 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.</t>
+          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.
+STEM: Trồng cây không cần hạt (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1404,7 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Sinh sản của thực vật có hoa (Tiết 2)</t>
+          <t>Bài 14. Sự phát triển của cây con (Tiết 2)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -1428,25 +1434,16 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bài 14. Sự phát triển của cây con (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 14. Sự phát triển của cây con (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.
-STEM: Trồng cây không cần hạt (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
-        </is>
-      </c>
+      <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1463,10 +1460,14 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bài 14. Sự phát triển của cây con (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Bài 15. Sinh sản của động vật (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>30</t>
@@ -1493,7 +1494,7 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bài 14. Sự phát triển của cây con (Tiết 3)</t>
+          <t>Bài 15. Sinh sản của động vật (Tiết 2)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -1502,7 +1503,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1519,7 +1524,7 @@
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Sinh sản của động vật (Tiết 1)</t>
+          <t>Bài 16. Vòng đời và sự phát triển của động vật (Tiết 1)</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1534,7 +1539,8 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.</t>
+          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.
+STEM: Vòng đời của động vật (Khoa học – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1559,7 @@
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Sinh sản của động vật (Tiết 2)</t>
+          <t>Bài 16. Vòng đời và sự phát triển của động vật (Tiết 2)</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -1576,14 +1582,14 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối học kì I</t>
+          <t>Bài 17. Ôn tập chủ đề Thực vật và động vật</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1596,11 +1602,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.</t>
-        </is>
-      </c>
+      <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1617,7 +1619,7 @@
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì cuối học kì I</t>
+          <t>Ôn tập học kì I</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1640,19 +1642,19 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Vòng đời và sự phát triển của động vật (Tiết 1)</t>
+          <t>Kiểm tra định kì cuối học kì I</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -1660,12 +1662,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.
-STEM: Vòng đời của động vật (Khoa học – Mĩ thuật) — dạy thay cho tiết này.</t>
-        </is>
-      </c>
+      <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -1675,17 +1672,21 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Vòng đời và sự phát triển của động vật (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+          <t>Bài 18. Vi khuẩn xung quanh chúng ta (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>37</t>
@@ -1693,7 +1694,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS kiểm chứng được kết quả nhận diện của ứng dụng bằng đặc điểm trong SGK.</t>
+          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.</t>
         </is>
       </c>
     </row>
@@ -1705,27 +1706,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Vi khuẩn</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Ôn tập chủ đề Thực vật và động vật</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 18. Vi khuẩn xung quanh chúng ta (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1742,7 +1743,7 @@
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Vi khuẩn xung quanh chúng ta (Tiết 1)</t>
+          <t>Bài 19. Vi khuẩn có ích trong chế biến thực phẩm (Tiết 1)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -1757,7 +1758,8 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.</t>
+          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.
+STEM: Vi khuẩn có ích trong chế biến thực phẩm (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1778,7 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Vi khuẩn xung quanh chúng ta (Tiết 2)</t>
+          <t>Bài 19. Vi khuẩn có ích trong chế biến thực phẩm (Tiết 2)</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -1806,7 +1808,7 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Vi khuẩn có ích trong chế biến thực phẩm (Tiết 1)</t>
+          <t>Bài 20. Vi khuẩn gây bệnh ở người và cách phòng tránh (Tiết 1)</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -1822,7 +1824,7 @@
       <c r="H44" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.
-STEM: Vi khuẩn có ích trong chế biến thực phẩm (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1843,7 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Vi khuẩn có ích trong chế biến thực phẩm (Tiết 2)</t>
+          <t>Bài 20. Vi khuẩn gây bệnh ở người và cách phòng tránh (Tiết 2)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -1871,12 +1873,12 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bài 20. Vi khuẩn gây bệnh ở người và cách phòng tránh (Tiết 1)</t>
+          <t>Bài 21. Ôn tập chủ đề Vi khuẩn</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -1884,12 +1886,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
-        </is>
-      </c>
+      <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1899,17 +1896,21 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Vi khuẩn</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bài 20. Vi khuẩn gây bệnh ở người và cách phòng tránh (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+          <t>Bài 22. Sự hình thành cơ thể người (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
           <t>44</t>
@@ -1917,7 +1918,8 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2b: HS quan sát hình ảnh hiển vi, tra cứu có đối chiếu SGK và ghi rõ nguồn thông tin.</t>
+          <t>Năng lực số 1.1 CB2c: HS quan sát sơ đồ động về các giai đoạn phát triển.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -1929,27 +1931,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Vi khuẩn</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Ôn tập chủ đề Vi khuẩn</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 22. Sự hình thành cơ thể người (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS quan sát sơ đồ động về các giai đoạn phát triển.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -1966,12 +1968,12 @@
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Sự hình thành cơ thể người (Tiết 1)</t>
+          <t>Bài 23. Các giai đoạn phát triển chính của con người (Tiết 1)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -1981,8 +1983,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát sơ đồ động về các giai đoạn phát triển.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+          <t>Năng lực số 1.1 CB2c: HS quan sát sơ đồ động về các giai đoạn phát triển.</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2002,7 @@
       <c r="D50" s="4" t="inlineStr"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Sự hình thành cơ thể người (Tiết 2)</t>
+          <t>Bài 23. Các giai đoạn phát triển chính của con người (Tiết 2)</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -2031,24 +2032,16 @@
       <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Các giai đoạn phát triển chính của con người (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 23. Các giai đoạn phát triển chính của con người (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát sơ đồ động về các giai đoạn phát triển.</t>
-        </is>
-      </c>
+      <c r="H51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2065,10 +2058,14 @@
       <c r="D52" s="4" t="inlineStr"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Các giai đoạn phát triển chính của con người (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
+          <t>Bài 24. Nam và nữ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
           <t>49</t>
@@ -2076,7 +2073,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát sơ đồ động về các giai đoạn phát triển.</t>
+          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2092,7 @@
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Các giai đoạn phát triển chính của con người (Tiết 3)</t>
+          <t>Bài 24. Nam và nữ (Tiết 2)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -2104,7 +2101,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2121,12 +2122,12 @@
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Nam và nữ (Tiết 1)</t>
+          <t>Bài 25. Chăm sóc sức khoẻ tuổi dậy thì (Tiết 1)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2136,7 +2137,9 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
+          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.
+STEM: Cẩm nang chăm sóc sức khoẻ tuổi dậy thì (Khoa học – Mĩ thuật) — dạy thay cho tiết này.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2158,7 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Nam và nữ (Tiết 2)</t>
+          <t>Bài 25. Chăm sóc sức khoẻ tuổi dậy thì (Tiết 2)</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
@@ -2178,27 +2181,27 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì II</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 25. Chăm sóc sức khoẻ tuổi dậy thì (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -2215,12 +2218,12 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Chăm sóc sức khoẻ tuổi dậy thì (Tiết 1)</t>
+          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 1)</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>4 tiết</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -2230,9 +2233,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.
-STEM: Cẩm nang chăm sóc sức khoẻ tuổi dậy thì (Khoa học – Mĩ thuật) — dạy thay cho tiết này.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2252,7 @@
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Chăm sóc sức khoẻ tuổi dậy thì (Tiết 2)</t>
+          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 2)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
@@ -2281,7 +2282,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Chăm sóc sức khoẻ tuổi dậy thì (Tiết 3)</t>
+          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 3)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -2311,14 +2312,10 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>4 tiết</t>
-        </is>
-      </c>
+          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 4)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr">
         <is>
           <t>57</t>
@@ -2345,20 +2342,20 @@
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
+          <t>Bài 27. Ôn tập chủ đề Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2368,17 +2365,21 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
+          <t>Bài 28. Chức năng của môi trường đối với sinh vật (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>59</t>
@@ -2386,7 +2387,8 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
+          <t>Năng lực số 1.1 CB2c: HS đọc được sự thay đổi của môi trường qua ảnh vệ tinh chụp nhiều thời điểm.
+KNS: KN sử dụng tiết kiệm tài nguyên, năng lượng trong sinh hoạt hằng ngày.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2400,14 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Phòng tránh bị xâm hại (Tiết 4)</t>
+          <t>Bài 28. Chức năng của môi trường đối với sinh vật (Tiết 2)</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -2416,7 +2418,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.2 CB2a: HS nêu được: ảnh và giọng nói trên mạng có thể do máy tạo giả, nên không gửi ảnh riêng tư cho bất kì ai.</t>
+          <t>Năng lực số 1.1 CB2c: HS đọc được sự thay đổi của môi trường qua ảnh vệ tinh chụp nhiều thời điểm.</t>
         </is>
       </c>
     </row>
@@ -2428,21 +2430,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Ôn tập chủ đề Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 28. Chức năng của môi trường đối với sinh vật (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>61</t>
@@ -2465,7 +2463,7 @@
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Chức năng của môi trường đối với sinh vật (Tiết 1)</t>
+          <t>Bài 29. Tác động của con người và một số biện pháp bảo vệ môi trường (Tiết 1)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2500,7 +2498,7 @@
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Chức năng của môi trường đối với sinh vật (Tiết 2)</t>
+          <t>Bài 29. Tác động của con người và một số biện pháp bảo vệ môi trường (Tiết 2)</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -2530,7 +2528,7 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Chức năng của môi trường đối với sinh vật (Tiết 3)</t>
+          <t>Bài 29. Tác động của con người và một số biện pháp bảo vệ môi trường (Tiết 3)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -2556,12 +2554,12 @@
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Tác động của con người và một số biện pháp bảo vệ môi trường (Tiết 1)</t>
+          <t>Bài 30. Ôn tập chủ đề Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -2569,12 +2567,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sự thay đổi của môi trường qua ảnh vệ tinh chụp nhiều thời điểm.
-KNS: KN sử dụng tiết kiệm tài nguyên, năng lượng trong sinh hoạt hằng ngày.</t>
-        </is>
-      </c>
+      <c r="H68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -2584,27 +2577,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Tác động của con người và một số biện pháp bảo vệ môi trường (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>Ôn tập cuối năm (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sự thay đổi của môi trường qua ảnh vệ tinh chụp nhiều thời điểm.</t>
-        </is>
-      </c>
+      <c r="H69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2614,17 +2607,21 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Tác động của con người và một số biện pháp bảo vệ môi trường (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
+          <t>Ôn tập cuối năm (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>67</t>
@@ -2640,14 +2637,14 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Ôn tập chủ đề Sinh vật và môi trường</t>
+          <t>Ôn tập cuối năm (Tiết 3)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2677,7 +2674,7 @@
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối năm học</t>
+          <t>Ôn tập cuối năm (Tiết 4)</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
